--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -593,19 +593,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e_Blackwall_AUS</t>
+          <t>e_Brisbane_AUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>grid node -- way/170832455-275 (Brisbane, 25 km)</t>
+          <t>grid node -- way/172587651-275 (Brisbane, 30 km)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -703,31 +703,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_Palmerston_AUS</t>
+          <t>e_Tarong_AUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>grid node -- way/174441055-220 (Launceston, 41 km)</t>
+          <t>grid node -- way/170709510-275 (Toowoomba, 87 km)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_CentralCoast_AUS</t>
+          <t>e_Palmerston_AUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>grid node -- AU73-330 (Central Coast, 39 km)</t>
+          <t>grid node -- way/174441055-220 (Launceston, 41 km)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -743,16 +743,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_Armidale_AUS</t>
+          <t>e_CentralCoast_AUS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>grid node -- way/160201298-330 (Newcastle, 267 km)</t>
+          <t>grid node -- AU73-330 (Central Coast, 39 km)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_Tarong_AUS</t>
+          <t>e_Armidale_AUS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>grid node -- way/170709510-275 (Toowoomba, 87 km)</t>
+          <t>grid node -- way/160201298-330 (Newcastle, 267 km)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -893,12 +893,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_MountPiper_AUS</t>
+          <t>e_Dubbo_AUS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>grid node -- way/169408193-330 (Sydney, 122 km)</t>
+          <t>grid node -- way/169406848-330 (Central Coast, 226 km)</t>
         </is>
       </c>
       <c r="D14" t="n">

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -893,12 +893,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_Dubbo_AUS</t>
+          <t>e_MountPiper_AUS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>grid node -- way/169406848-330 (Central Coast, 226 km)</t>
+          <t>grid node -- way/169408193-330 (Sydney, 122 km)</t>
         </is>
       </c>
       <c r="D14" t="n">

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -718,16 +718,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_Palmerston_AUS</t>
+          <t>e_AUS42p8S146p2E_AUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>grid node -- way/174441055-220 (Launceston, 41 km)</t>
+          <t>grid node -- AU149-220 (Hobart, 94 km)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1049,7 +1049,21 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>e_Palmerston_AUS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>grid node -- way/174441055-220 (Launceston, 41 km)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="20">
       <c r="K20" t="inlineStr">
         <is>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -718,12 +718,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_AUS42p8S146p2E_AUS</t>
+          <t>e_Hobart_AUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>grid node -- AU149-220 (Hobart, 94 km)</t>
+          <t>grid node -- AU146-220 (Hobart, 50 km)</t>
         </is>
       </c>
       <c r="D10" t="n">

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -593,19 +593,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e_Brisbane_AUS</t>
+          <t>e_Ipswich_AUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>grid node -- way/172587651-275 (Brisbane, 30 km)</t>
+          <t>grid node -- way/170832455-275 (Brisbane, 25 km)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -703,31 +703,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_Tarong_AUS</t>
+          <t>e_Kingston_AUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>grid node -- way/170709510-275 (Toowoomba, 87 km)</t>
+          <t>grid node -- AU147-220 (Hobart, 11 km)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_Hobart_AUS</t>
+          <t>e_CentralCoast_AUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>grid node -- AU146-220 (Hobart, 50 km)</t>
+          <t>grid node -- AU73-330 (Central Coast, 39 km)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -743,16 +743,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_CentralCoast_AUS</t>
+          <t>e_Armidale_AUS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>grid node -- AU73-330 (Central Coast, 39 km)</t>
+          <t>grid node -- way/160201298-330 (Newcastle, 267 km)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_Armidale_AUS</t>
+          <t>e_Tarong_AUS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>grid node -- way/160201298-330 (Newcastle, 267 km)</t>
+          <t>grid node -- way/170709510-275 (Toowoomba, 87 km)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
